--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -489,25 +489,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -516,30 +508,20 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -553,25 +535,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,30 +554,20 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>4.2e-05</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.001655</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.000766</v>
       </c>
     </row>
     <row r="8">
@@ -612,30 +576,20 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -644,30 +598,20 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -676,30 +620,20 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>4.2e-05</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.001655</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.000766</v>
       </c>
     </row>
     <row r="11">
@@ -713,25 +647,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.002034</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.002034</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.001655</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.000766</v>
       </c>
     </row>
     <row r="12">
@@ -740,30 +666,20 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -772,30 +688,20 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -804,30 +710,20 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -836,30 +732,20 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -873,25 +759,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="17">
@@ -900,30 +778,20 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1001,25 +869,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="21">
@@ -1028,30 +888,20 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1060,30 +910,20 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1145,25 +985,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1177,10 +1009,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>1.6973</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1209,25 +1039,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="28">
@@ -1236,30 +1058,20 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1273,25 +1085,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="30">
@@ -1337,25 +1141,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1408,25 +1204,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1440,25 +1228,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1472,25 +1252,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1504,25 +1276,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1536,25 +1300,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1568,25 +1324,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1600,25 +1348,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1632,25 +1372,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1664,25 +1396,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1696,25 +1420,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1728,25 +1444,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1760,25 +1468,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1792,25 +1492,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1824,25 +1516,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1856,25 +1540,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0.250283</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.223197</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.195419</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.174601</v>
       </c>
     </row>
     <row r="49">
@@ -1888,25 +1564,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="3" t="n">
+        <v>0.250283</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.223197</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.195419</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.174601</v>
       </c>
     </row>
     <row r="50">
@@ -1920,25 +1588,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1952,25 +1612,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1984,25 +1636,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2016,25 +1660,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2048,25 +1684,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2112,25 +1740,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2144,25 +1764,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2176,25 +1788,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2208,25 +1812,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2240,25 +1836,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2272,25 +1860,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2368,25 +1948,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2400,25 +1972,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2432,25 +1996,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2464,25 +2020,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2520,25 +2068,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2552,25 +2092,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2584,25 +2116,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2616,25 +2140,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2648,25 +2164,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2680,25 +2188,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2712,25 +2212,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2744,25 +2236,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C76" s="3" t="n">
+        <v>0.007373</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.014233</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.014715</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.028655</v>
       </c>
     </row>
     <row r="77">
@@ -2776,25 +2260,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2808,25 +2284,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2840,25 +2308,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2904,25 +2364,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2936,25 +2388,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2968,25 +2412,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3000,25 +2436,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3032,25 +2460,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3128,25 +2548,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>0.338161</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.338161</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.34877</v>
       </c>
     </row>
     <row r="89">
@@ -3160,25 +2572,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3216,25 +2620,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3248,25 +2644,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3280,25 +2668,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3312,25 +2692,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.208964</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.180704</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.145946</v>
       </c>
     </row>
     <row r="95">
@@ -3344,25 +2716,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3376,25 +2740,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.208964</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.180704</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.145946</v>
       </c>
     </row>
     <row r="97">
@@ -3447,25 +2803,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.101657</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.033946</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="100">
@@ -3474,30 +2822,20 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3506,30 +2844,20 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3538,30 +2866,20 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3570,30 +2888,20 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.002889</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.000581</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="104">
@@ -3624,30 +2932,20 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3656,30 +2954,20 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.004161</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.003212</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.003971</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.001063</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.013957</v>
       </c>
     </row>
     <row r="107">
@@ -3688,30 +2976,20 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3720,30 +2998,20 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3752,30 +3020,20 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3784,30 +3042,20 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3816,30 +3064,20 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3848,30 +3086,20 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3880,30 +3108,20 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3912,30 +3130,20 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3944,30 +3152,20 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3976,30 +3174,20 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4008,30 +3196,20 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4040,30 +3218,20 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4072,15 +3240,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -4104,30 +3268,20 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4136,30 +3290,20 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4168,30 +3312,20 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4200,30 +3334,20 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4232,30 +3356,20 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4264,30 +3378,20 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4296,30 +3400,20 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4360,30 +3454,20 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.05123</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4420,10 +3504,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.149958</v>
@@ -4444,30 +3526,20 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4520,30 +3592,20 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4552,30 +3614,20 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-4.2e-05</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.098445</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.029975</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.027197</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-0.020801</v>
       </c>
     </row>
   </sheetData>
@@ -4589,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4738,10 +3790,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current total</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -4807,31 +3863,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Current total</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Share capital (Note 5)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.007373</v>
+        <v>0.338161</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.014233</v>
+        <v>0.338161</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.014715</v>
+        <v>0.34877</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.028655</v>
+        <v>0.34877</v>
       </c>
     </row>
     <row r="7">
@@ -4847,12 +3907,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Share capital (Note 5)</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4861,16 +3921,16 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.338161</v>
+        <v>-0.10586</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.338161</v>
+        <v>-0.139806</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.34877</v>
+        <v>-0.168066</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.34877</v>
+        <v>-0.202824</v>
       </c>
     </row>
     <row r="8">
@@ -4886,12 +3946,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>SHAREHOLDERS’ EQUITY total</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4900,16 +3960,16 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.10586</v>
+        <v>0.24291</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.139806</v>
+        <v>0.208964</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.168066</v>
+        <v>0.180704</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-0.202824</v>
+        <v>0.145946</v>
       </c>
     </row>
     <row r="9">
@@ -4925,7 +3985,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY total</t>
+          <t>Reserves (Note 5)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -4935,90 +3995,100 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.24291</v>
+        <v>0.010609</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.208964</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.180704</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.145946</v>
+        <v>0.010609</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.250283</v>
+        <v>-0.101657</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.223197</v>
+        <v>-0.033946</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.195419</v>
+        <v>-0.02826</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.174601</v>
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reserves (Note 5)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Prepaids</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.010609</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.010609</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002889</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.000581</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="12">
@@ -5029,31 +4099,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.101657</v>
+        <v>0.003212</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.033946</v>
+        <v>0.00686</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.02826</v>
+        <v>0.000482</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-0.034758</v>
+        <v>0.01394</v>
       </c>
     </row>
     <row r="13">
@@ -5069,28 +4143,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prepaids</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="5" t="n">
+        <v>-0.098445</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.002889</v>
+        <v>-0.029975</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.000581</v>
+        <v>-0.027197</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1.7e-05</v>
+        <v>-0.020801</v>
       </c>
     </row>
     <row r="14">
@@ -5106,12 +4182,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5119,17 +4195,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0.003212</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.00686</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.000482</v>
+        <v>-0.027197</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.01394</v>
+        <v>-0.020801</v>
       </c>
     </row>
     <row r="15">
@@ -5145,12 +4225,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5158,17 +4238,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>-0.098445</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-0.029975</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-0.027197</v>
+        <v>0.220308</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-0.020801</v>
+        <v>0.193111</v>
       </c>
     </row>
     <row r="16">
@@ -5184,12 +4268,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5208,10 +4292,10 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.027197</v>
+        <v>0.193111</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.020801</v>
+        <v>0.17231</v>
       </c>
     </row>
     <row r="17">
@@ -5222,39 +4306,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>0.220308</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0.193111</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -5265,17 +4347,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5283,21 +4365,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F18" s="5" t="n">
+        <v>-0.05123</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>0.193111</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>0.17231</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -5313,7 +4397,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital</t>
+          <t>Proceeds from share subscriptions receivable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5323,7 +4407,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -5354,17 +4438,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.05123</v>
+        <v>0.19877</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -5395,22 +4483,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Proceeds from share subscriptions receivable</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.100325</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.029975</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -5436,12 +4526,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5450,12 +4540,10 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.19877</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.149958</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.250283</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -5481,12 +4569,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5495,10 +4583,10 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.100325</v>
+        <v>0.250283</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.029975</v>
+        <v>0.220308</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -5519,29 +4607,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.149958</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.250283</v>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -5562,29 +4648,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.250283</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.220308</v>
+          <t>September 30, September</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -5605,17 +4689,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Loss for the period $ (101,657) $</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>2e-06</v>
+        <v>-0.004203</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5646,17 +4730,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>September 30, September</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 3,212</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.004161</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5687,17 +4775,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loss for the period $ (101,657) $</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Net cash used in operating activities (98,445)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>-0.004203</v>
+        <v>-4.2e-05</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5728,21 +4820,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 3,212</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of share capital 200,000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.004161</v>
+        <v>0.15</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5773,21 +4861,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (98,445)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>-4.2e-05</v>
+          <t>Share issue costs (51,230)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5823,12 +4909,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital 200,000</t>
+          <t>Proceeds from share subscriptions receivable 50,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" s="5" t="n">
-        <v>0.15</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5864,14 +4952,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Share issue costs (51,230)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities 198,770</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5907,14 +4997,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Proceeds from share subscriptions receivable 50,000</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash 100,325</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.149958</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5950,16 +5042,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 198,770</t>
+          <t>Cash, beginning of period 149,958</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.15</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5995,12 +5089,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Change in cash 100,325</t>
+          <t>Cash, end of period $ 250,283 $</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
@@ -6040,18 +5134,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash, beginning of period 149,958</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Supplemental cash flow information (Note</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>8e-06</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6077,87 +5165,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash, end of period $ 250,283 $</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.149958</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Administrative $</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.002993</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.006458</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.002625</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.000788</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information (Note</t>
+          <t>Filing and regulatory</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>8e-06</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.025159</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.007276</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.009041</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.008397999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -6173,26 +5245,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Administrative $</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.002993</v>
+        <v>0.001876</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.006458</v>
+        <v>0.001768</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.002625</v>
+        <v>0.001325</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.000788</v>
+        <v>0.000766</v>
       </c>
     </row>
     <row r="40">
@@ -6208,26 +5284,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Filing and regulatory</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.025159</v>
+        <v>0.070187</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.007276</v>
+        <v>0.012919</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.009041</v>
+        <v>0.008943</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.008397999999999999</v>
+        <v>0.022163</v>
       </c>
     </row>
     <row r="41">
@@ -6243,26 +5323,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.001876</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.001768</v>
+        <v>0.000266</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.001325</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0.000766</v>
+        <v>0.00033</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6278,30 +5366,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.070187</v>
+        <v>0.001442</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.012919</v>
+        <v>0.005259</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.008943</v>
+        <v>0.005996</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.022163</v>
+        <v>0.002643</v>
       </c>
     </row>
     <row r="43">
@@ -6317,30 +5401,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shareholder communication</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.000266</v>
+        <v>-0.033946</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.00033</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.02826</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="44">
@@ -6356,26 +5440,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Loss per common share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.001442</v>
+        <v>-2e-08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.005259</v>
+        <v>-1e-08</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.005996</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.002643</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="45">
@@ -6386,35 +5474,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-0.101657</v>
+        <v>5.052056</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.033946</v>
+        <v>6.000001</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-0.02826</v>
+        <v>6.000001</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.034758</v>
+        <v>6.000001</v>
       </c>
     </row>
     <row r="46">
@@ -6425,35 +5509,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>0.208964</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.139806</v>
       </c>
     </row>
     <row r="47">
@@ -6464,12 +5548,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Expiry of agent’s warrants - 10,609 (10,609)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -6478,17 +5562,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>5.052056</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>6.000001</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>6.000001</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>6.000001</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -6504,10 +5596,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -6524,10 +5620,10 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.208964</v>
+        <v>-0.02826</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-0.139806</v>
+        <v>-0.02826</v>
       </c>
     </row>
     <row r="49">
@@ -6543,7 +5639,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Expiry of agent’s warrants - 10,609 (10,609)</t>
+          <t>September 30, 2024 6,000,001 348,770 -</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -6562,15 +5658,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>0.180704</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.168066</v>
       </c>
     </row>
     <row r="50">
@@ -6586,14 +5678,10 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>September 30, 2025 6,000,001 $ 348,770 $ - $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -6610,10 +5698,10 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-0.02826</v>
+        <v>0.145946</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.02826</v>
+        <v>-0.202824</v>
       </c>
     </row>
     <row r="51">
@@ -6622,14 +5710,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>of shares Amount Reserves Deficit Total</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>September 30, 2024 6,000,001 348,770 -</t>
+          <t>Year ended September</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -6638,21 +5722,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>0.180704</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>-0.168066</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -6663,12 +5749,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>September 30, 2025 6,000,001 $ 348,770 $ - $</t>
+          <t>Administrative $ 2,625 $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -6677,21 +5763,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="5" t="n">
+        <v>0.006458</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n">
-        <v>0.145946</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>-0.202824</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -6700,10 +5788,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Year ended September</t>
+          <t>Filing and regulatory 9,041</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -6713,7 +5805,7 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.007276</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6744,17 +5836,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Administrative $ 2,625 $</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Office and miscellaneous 1,325</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.006458</v>
+        <v>0.001768</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6785,17 +5881,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Filing and regulatory 9,041</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Professional fees 8,943</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.007276</v>
+        <v>0.012919</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6826,17 +5926,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 1,325</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Shareholder communication 330</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.001768</v>
+        <v>0.000266</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6867,21 +5971,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Professional fees 8,943</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Transfer agent 5,996</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.012919</v>
+        <v>0.005259</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6912,17 +6012,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shareholder communication 330</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $ (28,260) $</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.000266</v>
+        <v>-0.033946</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6953,7 +6057,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Transfer agent 5,996</t>
+          <t>Loss per common share – basic and diluted $ (0.00) $</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -6963,7 +6067,7 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.005259</v>
+        <v>-1e-08</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6989,26 +6093,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $ (28,260) $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted 6,000,001</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.033946</v>
+        <v>6.000001</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7034,12 +6134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $ (0.00) $</t>
+          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ (105,860) $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -7049,7 +6149,7 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.24291</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7075,12 +6175,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted 6,000,001</t>
+          <t>Loss for the year - - - (33,946)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -7090,7 +6190,7 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>6.000001</v>
+        <v>-0.033946</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7121,7 +6221,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ (105,860) $</t>
+          <t>September 30, 2023 6,000,001 338,161 10,609 (139,806)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -7131,7 +6231,7 @@
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.24291</v>
+        <v>0.208964</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7162,7 +6262,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (33,946)</t>
+          <t>Expiry of agent’s warrants - 10,609 (10,609) -</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -7171,8 +6271,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>-0.033946</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7203,7 +6305,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>September 30, 2023 6,000,001 338,161 10,609 (139,806)</t>
+          <t>Loss for the year - - - (28,260)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7213,7 +6315,7 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.208964</v>
+        <v>-0.02826</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7244,7 +6346,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Expiry of agent’s warrants - 10,609 (10,609) -</t>
+          <t>September 30, 2024 6,000,001 $ 348,770 $ - $ (168,066) $</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -7253,10 +6355,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>0.180704</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -7282,12 +6382,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares Amount Reserves receivable Deficit Total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (28,260)</t>
+          <t>September 30, 2021 4,000,001 $ 199,370 $ - $ (50,000) $</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7297,12 +6397,10 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.02826</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.145167</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -7323,12 +6421,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares Amount Reserves receivable Deficit Total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>September 30, 2024 6,000,001 $ 348,770 $ - $ (168,066) $</t>
+          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - -</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7338,7 +6436,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.180704</v>
+        <v>0.2</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -7369,7 +6467,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>September 30, 2021 4,000,001 $ 199,370 $ - $ (50,000) $</t>
+          <t>Share issue costs - (50,600) - -</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7379,10 +6477,12 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.145167</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>-0.004203</v>
+        <v>-0.0506</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7408,7 +6508,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - -</t>
+          <t>Issuance of agent’s warrants - (10,609) 10,609 -</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7417,8 +6517,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>0.2</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -7449,7 +6551,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Share issue costs - (50,600) - -</t>
+          <t>Share subscriptions received - - - 50,000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7459,7 +6561,7 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.0506</v>
+        <v>0.05</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -7490,24 +6592,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Issuance of agent’s warrants - (10,609) 10,609 -</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" s="5" t="n">
+        <v>-0.101657</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -7533,7 +6635,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share subscriptions received - - - 50,000</t>
+          <t>September 30, 2022 6,000,001 338,161 10,609 -</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -7543,12 +6645,10 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.24291</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-0.10586</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -7574,24 +6674,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $ - $</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.101657</v>
+        <v>0.208964</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.101657</v>
+        <v>-0.139806</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -7612,25 +6708,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>September 30, 2022 6,000,001 338,161 10,609 -</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.24291</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-0.10586</v>
+      <c r="E75" s="5" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7651,25 +6749,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $ - $</t>
+          <t>September 30, September</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.208964</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>-0.139806</v>
+      <c r="E76" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -7690,17 +6790,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Administrative $ 2,993 $</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.000788</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7731,17 +6831,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>September 30, September</t>
+          <t>Filing and regulatory 25,159</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.000373</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7777,12 +6877,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Administrative $ 2,993 $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Office and miscellaneous 1,876</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
-        <v>0.000788</v>
+        <v>4.2e-05</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7818,12 +6922,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Filing and regulatory 25,159</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Professional fees 70,187</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
-        <v>0.000373</v>
+        <v>0.003</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7859,12 +6967,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 1,876</t>
+          <t>Transfer agent 1,442</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>4.2e-05</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7900,16 +7010,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Professional fees 70,187</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Loss and comprehensive loss for the period $ (101,657) $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.004203</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7945,14 +7051,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Transfer agent 1,442</t>
+          <t>Loss per common share – basic and diluted $ (0.02) $</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7983,17 +7087,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period $ (101,657) $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted 5,052,056</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>-0.004203</v>
+        <v>0.142858</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8024,17 +7128,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares Amount Reserves receivable Deficit Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $ (0.02) $</t>
+          <t>September 2, 2021 - $ - $ - $ - $ - $</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8065,17 +7171,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>shares Amount Reserves receivable Deficit Total</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted 5,052,056</t>
+          <t>Issuance of common shares (Note 5) 4,000,001 200,000 - (50,000) -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>0.142858</v>
+        <v>0.15</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8111,14 +7217,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>September 2, 2021 - $ - $ - $ - $ - $</t>
+          <t>Share issue costs - (630) - - -</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>-0.00063</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,12 +7258,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Issuance of common shares (Note 5) 4,000,001 200,000 - (50,000) -</t>
+          <t>Loss for the period - - - - (4,203)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" s="5" t="n">
-        <v>0.15</v>
+        <v>-0.004203</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8195,12 +7299,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Share issue costs - (630) - - -</t>
+          <t>September 30, 2021 4,000,001 199,370 - (50,000) (4,203)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
-        <v>-0.00063</v>
+        <v>0.145167</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8236,12 +7340,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Loss for the period - - - - (4,203)</t>
+          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - - -</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>-0.004203</v>
+        <v>0.2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8277,12 +7381,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>September 30, 2021 4,000,001 199,370 - (50,000) (4,203)</t>
+          <t>Share issue costs - (50,600) - - -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" s="5" t="n">
-        <v>0.145167</v>
+        <v>-0.0506</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8318,12 +7422,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - - -</t>
+          <t>Issuance of agent’s warrants - (10,609) 10,609 - -</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>0.2</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8359,12 +7465,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Share issue costs - (50,600) - - -</t>
+          <t>Share subscriptions received - - - 50,000 -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
-        <v>-0.0506</v>
+        <v>0.05</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8400,14 +7506,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Issuance of agent’s warrants - (10,609) 10,609 - -</t>
+          <t>Loss for the year - - - - (101,657)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8443,12 +7547,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share subscriptions received - - - 50,000 -</t>
+          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ - $ (105,860) $</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="n">
-        <v>0.05</v>
+        <v>0.24291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8466,88 +7570,6 @@
         </is>
       </c>
       <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Loss for the year - - - - (101,657)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ - $ (105,860) $</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>0.24291</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -431,6 +431,14 @@
   </sheetPr>
   <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -492,10 +492,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -538,10 +536,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -566,7 +562,7 @@
         <v>4.2e-05</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.002034</v>
+        <v>0.001876</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.002034</v>
@@ -610,16 +606,16 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.001442</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.005259</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.005996</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.002643</v>
       </c>
     </row>
     <row r="10">
@@ -632,16 +628,16 @@
         <v>4.2e-05</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.002034</v>
+        <v>0.003318</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.002034</v>
+        <v>0.007293</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.001655</v>
+        <v>0.007651</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.000766</v>
+        <v>0.003409</v>
       </c>
     </row>
     <row r="11">
@@ -650,22 +646,20 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-4.2e-05</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.002034</v>
+        <v>-0.003318</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.002034</v>
+        <v>-0.007293</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.001655</v>
+        <v>-0.007651</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.000766</v>
+        <v>-0.003409</v>
       </c>
     </row>
     <row r="12">
@@ -697,19 +691,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -762,13 +756,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.033946</v>
+        <v>-0.101657</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.033946</v>
@@ -787,19 +779,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -872,13 +864,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.033946</v>
+        <v>-0.101657</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.033946</v>
@@ -940,13 +930,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.033946</v>
+        <v>-0.101657</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.033946</v>
@@ -964,10 +952,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.02</v>
@@ -988,10 +974,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.02</v>
@@ -1012,13 +996,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>0.1401</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.6973</v>
+        <v>5.08285</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1042,13 +1024,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.033946</v>
+        <v>-0.101657</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.033946</v>
@@ -1088,13 +1068,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.033946</v>
+        <v>-0.101657</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.033946</v>
@@ -1144,10 +1122,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1207,10 +1183,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -1231,10 +1205,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1255,10 +1227,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
@@ -1279,10 +1249,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1303,10 +1271,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1327,10 +1293,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1351,10 +1315,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1375,10 +1337,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1399,10 +1359,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1423,10 +1381,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1447,10 +1403,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1471,10 +1425,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1495,10 +1447,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1519,10 +1469,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1543,10 +1491,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.157833</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.250283</v>
@@ -1567,10 +1513,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.157833</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.250283</v>
@@ -1591,10 +1535,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1615,10 +1557,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1639,10 +1579,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1663,10 +1601,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1687,10 +1623,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1743,10 +1677,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1767,10 +1699,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1791,10 +1721,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -1815,10 +1743,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1839,10 +1765,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1863,10 +1787,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1951,10 +1873,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1975,10 +1895,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1999,10 +1917,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -2023,10 +1939,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -2047,10 +1961,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.012666</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.007373</v>
@@ -2071,10 +1983,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -2095,10 +2005,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2119,10 +2027,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2143,10 +2049,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -2167,10 +2071,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -2191,10 +2093,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -2215,10 +2115,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2239,10 +2137,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>0.012666</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>0.007373</v>
@@ -2263,10 +2159,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2287,10 +2181,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2311,10 +2203,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2367,10 +2257,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -2391,10 +2279,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -2415,10 +2301,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -2439,10 +2323,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -2463,10 +2345,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -2551,10 +2431,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.19937</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.338161</v>
@@ -2575,10 +2453,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2599,10 +2475,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-0.10586</v>
@@ -2623,10 +2497,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2647,10 +2519,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -2671,10 +2541,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2695,10 +2563,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.145167</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.24291</v>
@@ -2719,10 +2585,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2743,10 +2607,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.145167</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.24291</v>
@@ -2806,10 +2668,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.101657</v>
@@ -3649,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3726,10 +3586,8 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>0.149958</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0.250283</v>
@@ -3806,10 +3664,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="5" t="n">
+        <v>0.157833</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0.250283</v>
@@ -3845,10 +3701,8 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="5" t="n">
+        <v>0.012666</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.007373</v>
@@ -3884,10 +3738,8 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.19937</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.338161</v>
@@ -3923,10 +3775,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-0.10586</v>
@@ -3962,10 +3812,8 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="5" t="n">
+        <v>0.145167</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.24291</v>
@@ -4022,81 +3870,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>-0.033946</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>-0.02826</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>-0.034758</v>
+          <t>Deferred financing fees</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>0.007875</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prepaids</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share subscriptions receivable (Note 5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>-0.002889</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0.000581</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1.7e-05</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4107,17 +3957,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4126,16 +3976,16 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.003212</v>
+        <v>-0.101657</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.00686</v>
+        <v>-0.033946</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.000482</v>
+        <v>-0.02826</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.01394</v>
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="13">
@@ -4151,12 +4001,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Prepaids</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4164,17 +4014,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>-0.098445</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.029975</v>
+        <v>-0.002889</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-0.027197</v>
+        <v>0.000581</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.020801</v>
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4190,12 +4042,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4203,21 +4055,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>0.003212</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.00686</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-0.027197</v>
+        <v>0.000482</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-0.020801</v>
+        <v>0.01394</v>
       </c>
     </row>
     <row r="15">
@@ -4233,12 +4081,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4246,21 +4094,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="5" t="n">
+        <v>-0.098445</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.029975</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.220308</v>
+        <v>-0.027197</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.193111</v>
+        <v>-0.020801</v>
       </c>
     </row>
     <row r="16">
@@ -4276,12 +4120,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4294,16 +4138,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="5" t="n">
+        <v>-0.029975</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.193111</v>
+        <v>-0.027197</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.17231</v>
+        <v>-0.020801</v>
       </c>
     </row>
     <row r="17">
@@ -4314,37 +4156,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.250283</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.220308</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.193111</v>
       </c>
     </row>
     <row r="18">
@@ -4355,17 +4197,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4373,23 +4215,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>-0.05123</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.220308</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.193111</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.17231</v>
       </c>
     </row>
     <row r="19">
@@ -4405,17 +4243,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Proceeds from share subscriptions receivable</t>
+          <t>Proceeds from issuance of share capital</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E19" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4446,12 +4282,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4460,7 +4296,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.19877</v>
+        <v>-0.05123</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4491,24 +4327,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Proceeds from share subscriptions receivable</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.100325</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.029975</v>
+        <v>0.05</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4534,24 +4368,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.149958</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.250283</v>
+        <v>0.19877</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4577,24 +4411,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.149958</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.250283</v>
+        <v>0.100325</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.220308</v>
+        <v>-0.029975</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4615,27 +4447,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.149958</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.250283</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4656,27 +4490,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>September 30, September</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.250283</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.220308</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4702,17 +4538,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loss for the period $ (101,657) $</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.004203</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4743,7 +4581,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 3,212</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4754,10 +4592,8 @@
       <c r="E27" s="5" t="n">
         <v>0.004161</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="5" t="n">
+        <v>0.003212</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4788,7 +4624,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (98,445)</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4799,10 +4635,8 @@
       <c r="E28" s="5" t="n">
         <v>-4.2e-05</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="5" t="n">
+        <v>-0.098445</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4833,17 +4667,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital 200,000</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.149958</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4874,19 +4712,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Share issue costs (51,230)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.149958</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.250283</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4907,221 +4745,179 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Proceeds from share subscriptions receivable 50,000</t>
+          <t>Administrative $</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>0.000788</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.002993</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.006458</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.002625</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.000788</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities 198,770</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Filing and regulatory</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000373</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.025159</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.007276</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.009041</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.008397999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Change in cash 100,325</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.149958</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.2e-05</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.001876</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.001325</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.000766</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash, beginning of period 149,958</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.070187</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.012919</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.008943</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0.022163</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash, end of period $ 250,283 $</t>
+          <t>Shareholder communication</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.149958</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="5" t="n">
+        <v>0.000266</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.00033</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -5132,42 +4928,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information (Note</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" s="5" t="n">
-        <v>8e-06</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.001442</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.005259</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.005996</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.002643</v>
       </c>
     </row>
     <row r="37">
@@ -5183,26 +4977,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Administrative $</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.002993</v>
+        <v>-0.101657</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.006458</v>
+        <v>-0.033946</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.002625</v>
+        <v>-0.02826</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.000788</v>
+        <v>-0.034758</v>
       </c>
     </row>
     <row r="38">
@@ -5218,26 +5016,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Filing and regulatory</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per common share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.025159</v>
+        <v>-2e-08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.007276</v>
+        <v>-1e-08</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.009041</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.008397999999999999</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="39">
@@ -5248,35 +5048,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>0.142858</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.001876</v>
+        <v>5.052056</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.001768</v>
+        <v>6.000001</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.001325</v>
+        <v>6.000001</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.000766</v>
+        <v>6.000001</v>
       </c>
     </row>
     <row r="40">
@@ -5287,35 +5081,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>0.070187</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.012919</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.008943</v>
+        <v>0.208964</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.022163</v>
+        <v>-0.139806</v>
       </c>
     </row>
     <row r="41">
@@ -5326,19 +5120,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shareholder communication</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Expiry of agent’s warrants - 10,609 (10,609)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5349,11 +5139,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>0.000266</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.00033</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5369,31 +5163,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.001442</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.005259</v>
+        <v>-0.033946</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.005996</v>
+        <v>-0.02826</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.002643</v>
+        <v>-0.02826</v>
       </c>
     </row>
     <row r="43">
@@ -5404,35 +5204,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>September 30, 2024 6,000,001 348,770 -</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.033946</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>-0.02826</v>
+        <v>0.180704</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-0.034758</v>
+        <v>-0.168066</v>
       </c>
     </row>
     <row r="44">
@@ -5443,35 +5243,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>September 30, 2025 6,000,001 $ 348,770 $ - $</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0</v>
+        <v>0.145946</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.202824</v>
       </c>
     </row>
     <row r="45">
@@ -5482,12 +5282,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -5496,17 +5296,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>5.052056</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>6.000001</v>
+        <v>0.24291</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>6.000001</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>6.000001</v>
+        <v>-0.10586</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -5517,12 +5321,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $</t>
+          <t>September 30, 2023 6,000,001 338,161 10,609</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5536,16 +5340,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G46" s="5" t="n">
+        <v>0.208964</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.208964</v>
-      </c>
-      <c r="I46" s="5" t="n">
         <v>-0.139806</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -5556,12 +5360,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares         Amount         Reserves               Deficit               Total</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Expiry of agent’s warrants - 10,609 (10,609)</t>
+          <t>September 30, 2024 6,000,001 $ 348,770 $ - $</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5575,15 +5379,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="5" t="n">
+        <v>0.180704</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.168066</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5599,39 +5399,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>September 30, 2021 4,000,001 $ 199,370 $ - $ (50,000) $</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>-0.02826</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>-0.02826</v>
+      <c r="F48" s="5" t="n">
+        <v>0.145167</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.004203</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -5642,12 +5438,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>September 30, 2024 6,000,001 348,770 -</t>
+          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - -</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -5656,21 +5452,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n">
-        <v>0.180704</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-0.168066</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -5681,12 +5479,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>September 30, 2025 6,000,001 $ 348,770 $ - $</t>
+          <t>Share issue costs - (50,600) - -</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -5695,21 +5493,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>-0.0506</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="5" t="n">
-        <v>0.145946</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>-0.202824</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -5718,10 +5518,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Year ended September</t>
+          <t>Issuance of agent’s warrants - (10,609) 10,609 -</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5730,8 +5534,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>3e-05</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5757,12 +5563,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Administrative $ 2,625 $</t>
+          <t>Share subscriptions received - - - 50,000</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -5772,7 +5578,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.006458</v>
+        <v>0.05</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -5798,27 +5604,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Filing and regulatory 9,041</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.007276</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.101657</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -5839,31 +5647,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 1,325</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>September 30, 2022 6,000,001 338,161 10,609 -</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.001768</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.24291</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.10586</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -5884,31 +5686,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>of shares       Amount         Reserves        receivable             Deficit               Total</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Professional fees 8,943</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $ - $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.012919</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.208964</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.139806</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5934,21 +5730,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shareholder communication 330</t>
+          <t>Loss and comprehensive loss for the period $</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.000266</v>
+        <v>-0.101657</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5974,12 +5768,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Transfer agent 5,996</t>
+          <t>September 2, 2021 - $ - $ - $ - $</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5988,8 +5782,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.005259</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6015,26 +5811,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $ (28,260) $</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.033946</v>
+          <t>Issuance of common shares (Note 5) 4,000,001 200,000 - (50,000)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6060,22 +5852,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $ (0.00) $</t>
+          <t>Share issue costs - (630) - -</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="E59" s="5" t="n">
+        <v>-0.00063</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6101,22 +5893,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted 6,000,001</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the period - - - -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.004203</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>6.000001</v>
+        <v>-0.004203</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6142,22 +5936,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ (105,860) $</t>
+          <t>September 30, 2021 4,000,001 199,370 - (50,000)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="5" t="n">
+        <v>0.145167</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.24291</v>
+        <v>-0.004203</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6183,22 +5975,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (33,946)</t>
+          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - -</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.033946</v>
+      <c r="E62" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6224,22 +6016,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>September 30, 2023 6,000,001 338,161 10,609 (139,806)</t>
+          <t>Share issue costs - (50,600) - -</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.208964</v>
+      <c r="E63" s="5" t="n">
+        <v>-0.0506</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6265,12 +6057,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Expiry of agent’s warrants - 10,609 (10,609) -</t>
+          <t>Issuance of agent’s warrants - (10,609) 10,609 -</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -6308,22 +6100,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (28,260)</t>
+          <t>Share subscriptions received - - - 50,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>-0.02826</v>
+      <c r="E65" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6349,22 +6141,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>September 30, 2024 6,000,001 $ 348,770 $ - $ (168,066) $</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>-0.101657</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.180704</v>
+        <v>-0.101657</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -6390,25 +6184,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>shares       Amount          Reserves        receivable             Deficit              Total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>September 30, 2021 4,000,001 $ 199,370 $ - $ (50,000) $</t>
+          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ - $</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="5" t="n">
+        <v>0.24291</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.145167</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-0.004203</v>
+        <v>-0.10586</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -6429,12 +6223,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - -</t>
+          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -6443,23 +6237,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0.2</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H68" s="5" t="n">
+        <v>0.208964</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>-0.139806</v>
       </c>
     </row>
     <row r="69">
@@ -6470,12 +6262,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Share issue costs - (50,600) - -</t>
+          <t>Expiry of agent’s warrants - 10,609 (10,609)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6484,8 +6276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>-0.0506</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6511,15 +6305,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Issuance of agent’s warrants - (10,609) 10,609 -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6535,15 +6333,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.02826</v>
       </c>
     </row>
     <row r="71">
@@ -6554,12 +6348,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Share subscriptions received - - - 50,000</t>
+          <t>September 30, 2024 6,000,001 348,770 -</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -6568,23 +6362,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>0.05</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H71" s="5" t="n">
+        <v>0.180704</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>-0.168066</v>
       </c>
     </row>
     <row r="72">
@@ -6595,992 +6387,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
+          <t>of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>September 30, 2025 6,000,001 $ 348,770 $ - $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>September 30, 2022 6,000,001 338,161 10,609 -</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0.24291</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>-0.10586</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>of shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>September 30, 2023 6,000,001 $ 338,161 $ 10,609 $ - $</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>0.208964</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-0.139806</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>incorporation on</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>incorporation on</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>September 30, September</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Administrative $ 2,993 $</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>0.000788</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Filing and regulatory 25,159</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>0.000373</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Office and miscellaneous 1,876</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>4.2e-05</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Professional fees 70,187</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Transfer agent 1,442</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Loss and comprehensive loss for the period $ (101,657) $</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>-0.004203</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Loss per common share – basic and diluted $ (0.02) $</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted 5,052,056</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.142858</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>September 2, 2021 - $ - $ - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Issuance of common shares (Note 5) 4,000,001 200,000 - (50,000) -</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Share issue costs - (630) - - -</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>-0.00063</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Loss for the period - - - - (4,203)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>-0.004203</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>September 30, 2021 4,000,001 199,370 - (50,000) (4,203)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" s="5" t="n">
-        <v>0.145167</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Issuance of common shares (Note 5) 2,000,000 200,000 - - -</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Share issue costs - (50,600) - - -</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>-0.0506</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Issuance of agent’s warrants - (10,609) 10,609 - -</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Share subscriptions received - - - 50,000 -</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Loss for the year - - - - (101,657)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>-0.101657</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>shares Amount Reserves receivable Deficit Total</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>September 30, 2022 6,000,001 $ 338,161 $ 10,609 $ - $ (105,860) $</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0.24291</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.145946</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>-0.202824</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.010609</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.010609</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -3844,7 +3844,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.149958</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.250283</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.220308</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.193111</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.17231</v>
       </c>
     </row>
     <row r="35">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.149958</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.250283</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.220308</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.193111</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.17231</v>
       </c>
     </row>
     <row r="37">
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157833</v>
+        <v>0.007875</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.250283</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.223197</v>
+        <v>0.002889</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.195419</v>
+        <v>0.002308</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.174601</v>
+        <v>0.002291</v>
       </c>
     </row>
     <row r="49">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PCP.P.xlsx
+++ b/output/pdf_financials_xlsx/PCP.P.xlsx
@@ -1940,19 +1940,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.010875</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.024797</v>
       </c>
     </row>
     <row r="68">
